--- a/test_vlm_evalkit_results/levanter_vlm_ChartQA_TEST.xlsx
+++ b/test_vlm_evalkit_results/levanter_vlm_ChartQA_TEST.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>index</t>
   </si>
@@ -61,18 +61,6 @@
     <t>How many more people felt inspired frequently than depressed frequently?</t>
   </si>
   <si>
-    <t>What is the value of Slovenia in the graph?</t>
-  </si>
-  <si>
-    <t>What is the difference in value between Green bar and Orange bar?</t>
-  </si>
-  <si>
-    <t>What's the lefmost value of bar in China?</t>
-  </si>
-  <si>
-    <t>What's the average of all the values in the green bars (round to one decimal)?</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -103,19 +91,25 @@
     <t>0.03</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0.08</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>21.6</t>
-  </si>
-  <si>
     <t>test_human</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>Anxious</t>
   </si>
 </sst>
 </file>
@@ -473,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -501,10 +495,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -515,10 +512,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -529,10 +529,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -543,10 +546,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
         <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -557,10 +563,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -571,10 +580,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -585,10 +597,13 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -599,10 +614,13 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -613,10 +631,13 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -627,66 +648,13 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
